--- a/r4-ELGA-e-Medikation-Review_Architektur/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-Review_Architektur/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:41:29+00:00</t>
+    <t>2026-06-22T13:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -709,7 +709,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
